--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.80.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.80.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.80.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.80.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -609,24 +609,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: ç™¼</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+4F1A CJK UNIFIED IDEOGRAPH-4F1A | isolated marker/symbol line :: 会</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Â« last of several answersâ€™ has been filed, here mean-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]73</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]73</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L20: symbol-only separator/garbage line :: 1850,</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+4F1A CJK UNIFIED IDEOGRAPH-4F1A | isolated marker/symbol line :: 会</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L53: symbol-only separator/garbage line :: 1850,</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]73</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -678,22 +682,26 @@
           <t>L60: line starts with digit/letter garbage token | suspicious token(s): 0the (letter/digit mix) :: 0the</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+767C CJK UNIFIED IDEOGRAPH-767C | isolated marker/symbol line :: 發</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ filed</t>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • filed</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: o.</t>
+          <t>L20: symbol-only separator/garbage line :: 1850,</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "the" vs "1 0the" :: 1</t>
+          <t>L53: symbol-only separator/garbage line :: 1850,</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -736,25 +744,29 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 73</t>
+          <t>L37: isolated marker/symbol line :: o.</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L77: symbol-only separator/garbage line :: 586;</t>
+          <t>L58: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "the" vs "1 0the" :: 1</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • filed</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -770,7 +782,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -790,12 +802,12 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L66: symbol-only separator/garbage line :: 586;</t>
+          <t>L41: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: symbol-only separator/garbage line :: 586;</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -837,12 +849,12 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 2</t>
+          <t>L66: symbol-only separator/garbage line :: 586;</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: a</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -882,10 +894,14 @@
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+767C CJK UNIFIED IDEOGRAPH-767C | isolated marker/symbol line :: 發</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: I</t>
+          <t>L99: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -925,8 +941,16 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
-      <c r="O8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L124: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>L101: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
@@ -985,7 +1009,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1029,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1063,12 +1087,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1146,7 +1170,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
